--- a/public/files/resources/tools/tools/kpi-sheet-template.xlsx
+++ b/public/files/resources/tools/tools/kpi-sheet-template.xlsx
@@ -85,7 +85,7 @@
     <t xml:space="preserve">「はじめに入力」と月別の計画は、KPI管理表メーカーで入れた数字です。実績は空なので、毎月入れてください。Excelで開いて数字が出ないときは「編集を有効にする」を押してください</t>
   </si>
   <si>
-    <t>計算式と判定の基準は、MKTG.AXの「数字の定義」に従います</t>
+    <t>計算式と判定の基準は、MeerKitLabの「数字の定義」に従います</t>
   </si>
   <si>
     <t>1. 実績の合計（自動）</t>
